--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107887</v>
+        <v>107889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107889</v>
+        <v>107891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150343</v>
       </c>
       <c r="B2" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107891</v>
+        <v>107904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150343</v>
       </c>
       <c r="B2" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107904</v>
+        <v>107906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107906</v>
+        <v>107910</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150343</v>
       </c>
       <c r="B2" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107910</v>
+        <v>107931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107931</v>
+        <v>107932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150343</v>
       </c>
       <c r="B2" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107932</v>
+        <v>107937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107937</v>
+        <v>107940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150343</v>
       </c>
       <c r="B2" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107940</v>
+        <v>107946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107946</v>
+        <v>107947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107947</v>
+        <v>107959</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107959</v>
+        <v>107960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107960</v>
+        <v>107963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30240-2026 artfynd.xlsx
+++ b/artfynd/A 30240-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137150343</v>
       </c>
       <c r="B2" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137150342</v>
       </c>
       <c r="B3" t="n">
-        <v>107963</v>
+        <v>107969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
